--- a/curation/draft/package17/R17_BC_Misc_Edits.xlsx
+++ b/curation/draft/package17/R17_BC_Misc_Edits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/llander_cdisc_org/Documents/Documents/CDISC/Package 17/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package17\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{A24D0F04-B67E-4B6D-8DA3-22CE819F3104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF7E0C75-2B55-4B97-AD84-43A2516F796B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F130C2C-74DC-4CA6-9701-CD5D17CD5D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F590C486-C613-40E0-BF06-47BB8CB37E44}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_TU_TR_Edits" sheetId="5" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">BC_Misc_Edits!$A$1:$R$165</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BC_TU_TR_Edits!$A$1:$R$77</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3364" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3420" uniqueCount="448">
   <si>
     <t>package_date</t>
   </si>
@@ -1338,13 +1338,61 @@
   </si>
   <si>
     <t>Changed result_scale to Nominal from Ordinal</t>
+  </si>
+  <si>
+    <t>EudraVigilance Sender Organization</t>
+  </si>
+  <si>
+    <t>C126090</t>
+  </si>
+  <si>
+    <t>C93874</t>
+  </si>
+  <si>
+    <t>Trial Summary</t>
+  </si>
+  <si>
+    <t>EVSNDORG</t>
+  </si>
+  <si>
+    <t>The name of the group or institution that is transmitting an adverse drug reaction report to the EudraVigilance system.</t>
+  </si>
+  <si>
+    <t>C49691</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter</t>
+  </si>
+  <si>
+    <t>C83447</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Value</t>
+  </si>
+  <si>
+    <t>Pharmaco</t>
+  </si>
+  <si>
+    <t>C117460</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Name of the Reference Terminology</t>
+  </si>
+  <si>
+    <t>C83445</t>
+  </si>
+  <si>
+    <t>Trial Summary Parameter Code</t>
+  </si>
+  <si>
+    <t>EudraVigilance Sender Organization Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1838,17 +1886,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C984FF-E62A-4B57-AEF0-FD824E233583}">
   <dimension ref="A1:R77"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.9375" customWidth="1"/>
-    <col min="6" max="6" width="36.3515625" customWidth="1"/>
-    <col min="7" max="7" width="14.87890625" customWidth="1"/>
-    <col min="9" max="9" width="56.52734375" customWidth="1"/>
-    <col min="17" max="17" width="78.8203125" customWidth="1"/>
-    <col min="18" max="18" width="16.1171875" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="56.5703125" customWidth="1"/>
+    <col min="17" max="17" width="78.85546875" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="9" customFormat="1" ht="14.1" customHeight="1">
+    <row r="1" spans="1:18" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1904,7 +1952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="2" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -1951,7 +1999,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="3" spans="1:18" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -1998,7 +2046,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="4" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -2045,7 +2093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="5" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -2092,7 +2140,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -2139,7 +2187,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="7" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -2184,7 +2232,7 @@
       </c>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="8" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -2231,7 +2279,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="9" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -2278,7 +2326,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -2325,7 +2373,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="11" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -2372,7 +2420,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="12" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2422,7 +2470,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="13" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -2470,7 +2518,7 @@
       </c>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="14" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
@@ -2518,7 +2566,7 @@
       </c>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="15" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -2566,7 +2614,7 @@
       </c>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="16" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -2614,7 +2662,7 @@
       </c>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="17" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
@@ -2662,7 +2710,7 @@
       </c>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="18" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -2710,7 +2758,7 @@
       </c>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="19" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2758,7 +2806,7 @@
       </c>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="20" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -2804,7 +2852,7 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="21" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -2852,7 +2900,7 @@
       </c>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="22" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -2900,7 +2948,7 @@
       </c>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="23" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -2948,7 +2996,7 @@
       </c>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="24" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
@@ -2994,7 +3042,7 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="25" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -3042,7 +3090,7 @@
       </c>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="26" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -3090,7 +3138,7 @@
       </c>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="27" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -3138,7 +3186,7 @@
       </c>
       <c r="R27" s="2"/>
     </row>
-    <row r="28" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="28" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -3186,7 +3234,7 @@
       </c>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="29" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -3234,7 +3282,7 @@
       </c>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="30" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -3282,7 +3330,7 @@
       </c>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="31" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -3330,7 +3378,7 @@
       </c>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="32" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -3378,7 +3426,7 @@
       </c>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="33" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -3426,7 +3474,7 @@
       </c>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="34" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -3474,7 +3522,7 @@
       </c>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="35" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -3520,7 +3568,7 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="36" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -3566,7 +3614,7 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="37" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -3614,7 +3662,7 @@
       </c>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="38" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -3662,7 +3710,7 @@
       </c>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="39" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -3710,7 +3758,7 @@
       </c>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="40" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>36</v>
       </c>
@@ -3758,7 +3806,7 @@
       </c>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="41" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -3806,7 +3854,7 @@
       </c>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="42" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>36</v>
       </c>
@@ -3854,7 +3902,7 @@
       </c>
       <c r="R42" s="2"/>
     </row>
-    <row r="43" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="43" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3902,7 +3950,7 @@
       </c>
       <c r="R43" s="2"/>
     </row>
-    <row r="44" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="44" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>36</v>
       </c>
@@ -3950,7 +3998,7 @@
       </c>
       <c r="R44" s="2"/>
     </row>
-    <row r="45" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="45" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>36</v>
       </c>
@@ -3996,7 +4044,7 @@
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
     </row>
-    <row r="46" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="46" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>36</v>
       </c>
@@ -4044,7 +4092,7 @@
       </c>
       <c r="R46" s="2"/>
     </row>
-    <row r="47" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="47" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>36</v>
       </c>
@@ -4092,7 +4140,7 @@
       </c>
       <c r="R47" s="2"/>
     </row>
-    <row r="48" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="48" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
@@ -4140,7 +4188,7 @@
       </c>
       <c r="R48" s="2"/>
     </row>
-    <row r="49" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="49" spans="1:18" s="10" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>36</v>
       </c>
@@ -4188,7 +4236,7 @@
       </c>
       <c r="R49" s="2"/>
     </row>
-    <row r="50" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="50" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>36</v>
       </c>
@@ -4236,7 +4284,7 @@
       </c>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="51" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>36</v>
       </c>
@@ -4284,7 +4332,7 @@
       </c>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="52" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>36</v>
       </c>
@@ -4332,7 +4380,7 @@
       </c>
       <c r="R52" s="2"/>
     </row>
-    <row r="53" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="53" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>36</v>
       </c>
@@ -4380,7 +4428,7 @@
       </c>
       <c r="R53" s="2"/>
     </row>
-    <row r="54" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="54" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>36</v>
       </c>
@@ -4428,7 +4476,7 @@
       </c>
       <c r="R54" s="2"/>
     </row>
-    <row r="55" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="55" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>36</v>
       </c>
@@ -4476,7 +4524,7 @@
       </c>
       <c r="R55" s="2"/>
     </row>
-    <row r="56" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="56" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>36</v>
       </c>
@@ -4524,7 +4572,7 @@
       </c>
       <c r="R56" s="2"/>
     </row>
-    <row r="57" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="57" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>36</v>
       </c>
@@ -4570,7 +4618,7 @@
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
     </row>
-    <row r="58" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="58" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>36</v>
       </c>
@@ -4618,7 +4666,7 @@
       </c>
       <c r="R58" s="2"/>
     </row>
-    <row r="59" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="59" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>36</v>
       </c>
@@ -4666,7 +4714,7 @@
       </c>
       <c r="R59" s="2"/>
     </row>
-    <row r="60" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="60" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -4714,7 +4762,7 @@
       </c>
       <c r="R60" s="2"/>
     </row>
-    <row r="61" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="61" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -4762,7 +4810,7 @@
       </c>
       <c r="R61" s="2"/>
     </row>
-    <row r="62" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="62" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>36</v>
       </c>
@@ -4810,7 +4858,7 @@
       </c>
       <c r="R62" s="2"/>
     </row>
-    <row r="63" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="63" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>36</v>
       </c>
@@ -4858,7 +4906,7 @@
       </c>
       <c r="R63" s="2"/>
     </row>
-    <row r="64" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="64" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>36</v>
       </c>
@@ -4906,7 +4954,7 @@
       </c>
       <c r="R64" s="2"/>
     </row>
-    <row r="65" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="65" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>36</v>
       </c>
@@ -4954,7 +5002,7 @@
       </c>
       <c r="R65" s="2"/>
     </row>
-    <row r="66" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="66" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>36</v>
       </c>
@@ -5002,7 +5050,7 @@
       </c>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="67" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
@@ -5050,7 +5098,7 @@
       </c>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="68" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -5096,7 +5144,7 @@
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
     </row>
-    <row r="69" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="69" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
@@ -5142,7 +5190,7 @@
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="70" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
@@ -5190,7 +5238,7 @@
       </c>
       <c r="R70" s="2"/>
     </row>
-    <row r="71" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="71" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>36</v>
       </c>
@@ -5238,7 +5286,7 @@
       </c>
       <c r="R71" s="2"/>
     </row>
-    <row r="72" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="72" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>36</v>
       </c>
@@ -5286,7 +5334,7 @@
       </c>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="73" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>36</v>
       </c>
@@ -5334,7 +5382,7 @@
       </c>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="74" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>36</v>
       </c>
@@ -5382,7 +5430,7 @@
       </c>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="75" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>36</v>
       </c>
@@ -5430,7 +5478,7 @@
       </c>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="76" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>36</v>
       </c>
@@ -5478,7 +5526,7 @@
       </c>
       <c r="R76" s="2"/>
     </row>
-    <row r="77" spans="1:18" s="10" customFormat="1" ht="28.7">
+    <row r="77" spans="1:18" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -5733,17 +5781,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0A80D8-6C04-4D44-A5DD-9337CFFA755D}">
-  <dimension ref="A1:R165"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <dimension ref="A1:R169"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.29296875" customWidth="1"/>
-    <col min="6" max="6" width="33.46875" customWidth="1"/>
-    <col min="7" max="7" width="17.41015625" customWidth="1"/>
-    <col min="9" max="9" width="67.703125" customWidth="1"/>
-    <col min="10" max="10" width="13.1171875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="67.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="9" customFormat="1" ht="14.1" customHeight="1">
+    <row r="1" spans="1:18" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5799,7 +5848,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="2" spans="1:18" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
@@ -5855,7 +5904,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="3" spans="1:18" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -5906,7 +5955,7 @@
       </c>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="4" spans="1:18" s="11" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -5957,7 +6006,7 @@
       </c>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="5" spans="1:18" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
@@ -6013,7 +6062,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="6" spans="1:18" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -6066,7 +6115,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="7" spans="1:18" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -6117,7 +6166,7 @@
       </c>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:18" s="11" customFormat="1" ht="43">
+    <row r="8" spans="1:18" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -6168,7 +6217,7 @@
       </c>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="9" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -6218,7 +6267,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="10" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -6263,7 +6312,7 @@
       </c>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="11" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
@@ -6308,7 +6357,7 @@
       </c>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="12" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -6355,7 +6404,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="13" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -6402,7 +6451,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="14" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
@@ -6447,7 +6496,7 @@
       </c>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="15" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>36</v>
       </c>
@@ -6494,7 +6543,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="11" customFormat="1" ht="28.7">
+    <row r="16" spans="1:18" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -6539,7 +6588,7 @@
       </c>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="17" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>36</v>
       </c>
@@ -6584,7 +6633,7 @@
       </c>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="18" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>36</v>
       </c>
@@ -6631,7 +6680,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="19" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -6676,7 +6725,7 @@
       </c>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="20" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -6721,7 +6770,7 @@
       </c>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="21" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>36</v>
       </c>
@@ -6766,7 +6815,7 @@
       </c>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="22" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
@@ -6811,7 +6860,7 @@
       </c>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="23" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>36</v>
       </c>
@@ -6856,7 +6905,7 @@
       </c>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="24" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>36</v>
       </c>
@@ -6903,7 +6952,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="11" customFormat="1">
+    <row r="25" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
@@ -6950,7 +6999,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="11" customFormat="1">
+    <row r="26" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -6995,7 +7044,7 @@
       </c>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="27" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
@@ -7040,7 +7089,7 @@
       </c>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="28" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -7087,7 +7136,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="29" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -7132,7 +7181,7 @@
       </c>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="30" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -7179,7 +7228,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="31" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
@@ -7226,7 +7275,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="32" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>36</v>
       </c>
@@ -7271,7 +7320,7 @@
       </c>
       <c r="Q32" s="2"/>
     </row>
-    <row r="33" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="33" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
@@ -7318,7 +7367,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="34" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -7363,7 +7412,7 @@
       </c>
       <c r="Q34" s="2"/>
     </row>
-    <row r="35" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="35" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -7410,7 +7459,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="36" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
@@ -7457,7 +7506,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="37" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -7502,7 +7551,7 @@
       </c>
       <c r="Q37" s="2"/>
     </row>
-    <row r="38" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="38" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -7547,7 +7596,7 @@
       </c>
       <c r="Q38" s="2"/>
     </row>
-    <row r="39" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="39" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>36</v>
       </c>
@@ -7594,7 +7643,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="40" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>36</v>
       </c>
@@ -7639,7 +7688,7 @@
       </c>
       <c r="Q40" s="2"/>
     </row>
-    <row r="41" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="41" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>36</v>
       </c>
@@ -7684,7 +7733,7 @@
       </c>
       <c r="Q41" s="2"/>
     </row>
-    <row r="42" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="42" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>36</v>
       </c>
@@ -7731,7 +7780,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="43" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>36</v>
       </c>
@@ -7776,7 +7825,7 @@
       </c>
       <c r="Q43" s="2"/>
     </row>
-    <row r="44" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="44" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>36</v>
       </c>
@@ -7821,7 +7870,7 @@
       </c>
       <c r="Q44" s="2"/>
     </row>
-    <row r="45" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="45" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>36</v>
       </c>
@@ -7868,7 +7917,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="46" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>36</v>
       </c>
@@ -7915,7 +7964,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="47" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>36</v>
       </c>
@@ -7960,7 +8009,7 @@
       </c>
       <c r="Q47" s="2"/>
     </row>
-    <row r="48" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="48" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
@@ -8007,7 +8056,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="49" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>36</v>
       </c>
@@ -8052,7 +8101,7 @@
       </c>
       <c r="Q49" s="2"/>
     </row>
-    <row r="50" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="50" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>36</v>
       </c>
@@ -8099,7 +8148,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="51" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>36</v>
       </c>
@@ -8144,7 +8193,7 @@
       </c>
       <c r="Q51" s="2"/>
     </row>
-    <row r="52" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="52" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>36</v>
       </c>
@@ -8191,7 +8240,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="53" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>36</v>
       </c>
@@ -8236,7 +8285,7 @@
       </c>
       <c r="Q53" s="2"/>
     </row>
-    <row r="54" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="54" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>36</v>
       </c>
@@ -8283,7 +8332,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="55" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>36</v>
       </c>
@@ -8328,7 +8377,7 @@
       </c>
       <c r="Q55" s="2"/>
     </row>
-    <row r="56" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="56" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>36</v>
       </c>
@@ -8375,7 +8424,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="57" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>36</v>
       </c>
@@ -8420,7 +8469,7 @@
       </c>
       <c r="Q57" s="2"/>
     </row>
-    <row r="58" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="58" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>36</v>
       </c>
@@ -8467,7 +8516,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="59" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>36</v>
       </c>
@@ -8512,7 +8561,7 @@
       </c>
       <c r="Q59" s="2"/>
     </row>
-    <row r="60" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="60" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -8559,7 +8608,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="61" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -8606,7 +8655,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="62" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>36</v>
       </c>
@@ -8651,7 +8700,7 @@
       </c>
       <c r="Q62" s="2"/>
     </row>
-    <row r="63" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="63" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>36</v>
       </c>
@@ -8696,7 +8745,7 @@
       </c>
       <c r="Q63" s="2"/>
     </row>
-    <row r="64" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="64" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>36</v>
       </c>
@@ -8743,7 +8792,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="65" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>36</v>
       </c>
@@ -8788,7 +8837,7 @@
       </c>
       <c r="Q65" s="2"/>
     </row>
-    <row r="66" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="66" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>36</v>
       </c>
@@ -8835,7 +8884,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="67" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
@@ -8880,7 +8929,7 @@
       </c>
       <c r="Q67" s="2"/>
     </row>
-    <row r="68" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="68" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -8927,7 +8976,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="69" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
@@ -8972,7 +9021,7 @@
       </c>
       <c r="Q69" s="2"/>
     </row>
-    <row r="70" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="70" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
@@ -9019,7 +9068,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="71" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>36</v>
       </c>
@@ -9064,7 +9113,7 @@
       </c>
       <c r="Q71" s="2"/>
     </row>
-    <row r="72" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="72" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>36</v>
       </c>
@@ -9111,7 +9160,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="73" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>36</v>
       </c>
@@ -9156,7 +9205,7 @@
       </c>
       <c r="Q73" s="2"/>
     </row>
-    <row r="74" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="74" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>36</v>
       </c>
@@ -9203,7 +9252,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="75" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>36</v>
       </c>
@@ -9250,7 +9299,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="76" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>36</v>
       </c>
@@ -9295,7 +9344,7 @@
       </c>
       <c r="Q76" s="2"/>
     </row>
-    <row r="77" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="77" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -9342,7 +9391,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="78" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>36</v>
       </c>
@@ -9387,7 +9436,7 @@
       </c>
       <c r="Q78" s="2"/>
     </row>
-    <row r="79" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="79" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>36</v>
       </c>
@@ -9432,7 +9481,7 @@
       </c>
       <c r="Q79" s="2"/>
     </row>
-    <row r="80" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="80" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
@@ -9479,7 +9528,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="81" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>36</v>
       </c>
@@ -9524,7 +9573,7 @@
       </c>
       <c r="Q81" s="2"/>
     </row>
-    <row r="82" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="82" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>36</v>
       </c>
@@ -9571,7 +9620,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="83" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>36</v>
       </c>
@@ -9616,7 +9665,7 @@
       </c>
       <c r="Q83" s="2"/>
     </row>
-    <row r="84" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="84" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>36</v>
       </c>
@@ -9663,7 +9712,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="85" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>36</v>
       </c>
@@ -9710,7 +9759,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="86" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>36</v>
       </c>
@@ -9755,7 +9804,7 @@
       </c>
       <c r="Q86" s="2"/>
     </row>
-    <row r="87" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="87" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>36</v>
       </c>
@@ -9802,7 +9851,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="88" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>36</v>
       </c>
@@ -9847,7 +9896,7 @@
       </c>
       <c r="Q88" s="2"/>
     </row>
-    <row r="89" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="89" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>36</v>
       </c>
@@ -9892,7 +9941,7 @@
       </c>
       <c r="Q89" s="2"/>
     </row>
-    <row r="90" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="90" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>36</v>
       </c>
@@ -9939,7 +9988,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="91" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>36</v>
       </c>
@@ -9984,7 +10033,7 @@
       </c>
       <c r="Q91" s="2"/>
     </row>
-    <row r="92" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="92" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>36</v>
       </c>
@@ -10031,7 +10080,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="93" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>36</v>
       </c>
@@ -10076,7 +10125,7 @@
       </c>
       <c r="Q93" s="2"/>
     </row>
-    <row r="94" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="94" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>36</v>
       </c>
@@ -10123,7 +10172,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="95" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>36</v>
       </c>
@@ -10170,7 +10219,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="96" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>36</v>
       </c>
@@ -10215,7 +10264,7 @@
       </c>
       <c r="Q96" s="2"/>
     </row>
-    <row r="97" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="97" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>36</v>
       </c>
@@ -10262,7 +10311,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="98" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>36</v>
       </c>
@@ -10307,7 +10356,7 @@
       </c>
       <c r="Q98" s="2"/>
     </row>
-    <row r="99" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="99" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>36</v>
       </c>
@@ -10354,7 +10403,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="100" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>36</v>
       </c>
@@ -10399,7 +10448,7 @@
       </c>
       <c r="Q100" s="2"/>
     </row>
-    <row r="101" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="101" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>36</v>
       </c>
@@ -10444,7 +10493,7 @@
       </c>
       <c r="Q101" s="2"/>
     </row>
-    <row r="102" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="102" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>36</v>
       </c>
@@ -10491,7 +10540,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="103" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>36</v>
       </c>
@@ -10538,7 +10587,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="104" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>36</v>
       </c>
@@ -10583,7 +10632,7 @@
       </c>
       <c r="Q104" s="2"/>
     </row>
-    <row r="105" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="105" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>36</v>
       </c>
@@ -10628,7 +10677,7 @@
       </c>
       <c r="Q105" s="2"/>
     </row>
-    <row r="106" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="106" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>36</v>
       </c>
@@ -10675,7 +10724,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="107" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>36</v>
       </c>
@@ -10720,7 +10769,7 @@
       </c>
       <c r="Q107" s="2"/>
     </row>
-    <row r="108" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="108" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>36</v>
       </c>
@@ -10767,7 +10816,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="109" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>36</v>
       </c>
@@ -10814,7 +10863,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="110" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>36</v>
       </c>
@@ -10859,7 +10908,7 @@
       </c>
       <c r="Q110" s="2"/>
     </row>
-    <row r="111" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="111" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>36</v>
       </c>
@@ -10906,7 +10955,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="112" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>36</v>
       </c>
@@ -10951,7 +11000,7 @@
       </c>
       <c r="Q112" s="2"/>
     </row>
-    <row r="113" spans="1:17" s="11" customFormat="1">
+    <row r="113" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>36</v>
       </c>
@@ -10996,7 +11045,7 @@
       </c>
       <c r="Q113" s="2"/>
     </row>
-    <row r="114" spans="1:17" s="11" customFormat="1">
+    <row r="114" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>36</v>
       </c>
@@ -11043,7 +11092,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="115" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>36</v>
       </c>
@@ -11090,7 +11139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="116" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>36</v>
       </c>
@@ -11135,7 +11184,7 @@
       </c>
       <c r="Q116" s="2"/>
     </row>
-    <row r="117" spans="1:17" s="11" customFormat="1">
+    <row r="117" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>36</v>
       </c>
@@ -11182,7 +11231,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="11" customFormat="1">
+    <row r="118" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>36</v>
       </c>
@@ -11227,7 +11276,7 @@
       </c>
       <c r="Q118" s="2"/>
     </row>
-    <row r="119" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="119" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>36</v>
       </c>
@@ -11274,7 +11323,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="120" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>36</v>
       </c>
@@ -11319,7 +11368,7 @@
       </c>
       <c r="Q120" s="2"/>
     </row>
-    <row r="121" spans="1:17" s="11" customFormat="1">
+    <row r="121" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>36</v>
       </c>
@@ -11366,7 +11415,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="11" customFormat="1">
+    <row r="122" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>36</v>
       </c>
@@ -11411,7 +11460,7 @@
       </c>
       <c r="Q122" s="2"/>
     </row>
-    <row r="123" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="123" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>36</v>
       </c>
@@ -11456,7 +11505,7 @@
       </c>
       <c r="Q123" s="2"/>
     </row>
-    <row r="124" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="124" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>36</v>
       </c>
@@ -11503,7 +11552,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="125" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>36</v>
       </c>
@@ -11550,7 +11599,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="11" customFormat="1">
+    <row r="126" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>36</v>
       </c>
@@ -11595,7 +11644,7 @@
       </c>
       <c r="Q126" s="2"/>
     </row>
-    <row r="127" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="127" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>36</v>
       </c>
@@ -11640,7 +11689,7 @@
       </c>
       <c r="Q127" s="2"/>
     </row>
-    <row r="128" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="128" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>36</v>
       </c>
@@ -11687,7 +11736,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="11" customFormat="1" ht="143.35">
+    <row r="129" spans="1:17" s="11" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>36</v>
       </c>
@@ -11734,7 +11783,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="130" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>36</v>
       </c>
@@ -11781,7 +11830,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="131" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>36</v>
       </c>
@@ -11828,7 +11877,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="132" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>36</v>
       </c>
@@ -11873,7 +11922,7 @@
       </c>
       <c r="Q132" s="2"/>
     </row>
-    <row r="133" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="133" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>36</v>
       </c>
@@ -11920,7 +11969,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="134" spans="1:17" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>36</v>
       </c>
@@ -11965,7 +12014,7 @@
       </c>
       <c r="Q134" s="2"/>
     </row>
-    <row r="135" spans="1:17" s="11" customFormat="1" ht="86">
+    <row r="135" spans="1:17" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>36</v>
       </c>
@@ -12012,7 +12061,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="136" spans="1:17" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>36</v>
       </c>
@@ -12059,7 +12108,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="11" customFormat="1" ht="71.7">
+    <row r="137" spans="1:17" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>36</v>
       </c>
@@ -12106,7 +12155,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="11" customFormat="1" ht="86">
+    <row r="138" spans="1:17" s="11" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>36</v>
       </c>
@@ -12153,7 +12202,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="139" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>36</v>
       </c>
@@ -12198,7 +12247,7 @@
       </c>
       <c r="Q139" s="2"/>
     </row>
-    <row r="140" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="140" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>36</v>
       </c>
@@ -12245,7 +12294,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="11" customFormat="1" ht="57.35">
+    <row r="141" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>36</v>
       </c>
@@ -12292,7 +12341,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="142" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>36</v>
       </c>
@@ -12339,7 +12388,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="143" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>36</v>
       </c>
@@ -12384,7 +12433,7 @@
       </c>
       <c r="Q143" s="2"/>
     </row>
-    <row r="144" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="144" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>36</v>
       </c>
@@ -12431,7 +12480,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="145" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>36</v>
       </c>
@@ -12478,7 +12527,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="146" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>36</v>
       </c>
@@ -12525,7 +12574,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="11" customFormat="1" ht="57.35">
+    <row r="147" spans="1:17" s="11" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>36</v>
       </c>
@@ -12572,7 +12621,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="148" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>36</v>
       </c>
@@ -12619,7 +12668,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="149" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>36</v>
       </c>
@@ -12664,7 +12713,7 @@
       </c>
       <c r="Q149" s="2"/>
     </row>
-    <row r="150" spans="1:17" s="11" customFormat="1" ht="43">
+    <row r="150" spans="1:17" s="11" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>36</v>
       </c>
@@ -12711,7 +12760,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="151" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>36</v>
       </c>
@@ -12756,7 +12805,7 @@
       </c>
       <c r="Q151" s="2"/>
     </row>
-    <row r="152" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="152" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>36</v>
       </c>
@@ -12803,7 +12852,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="153" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>36</v>
       </c>
@@ -12848,7 +12897,7 @@
       </c>
       <c r="Q153" s="2"/>
     </row>
-    <row r="154" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="154" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>36</v>
       </c>
@@ -12893,7 +12942,7 @@
       </c>
       <c r="Q154" s="2"/>
     </row>
-    <row r="155" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="155" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>36</v>
       </c>
@@ -12938,7 +12987,7 @@
       </c>
       <c r="Q155" s="2"/>
     </row>
-    <row r="156" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="156" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>36</v>
       </c>
@@ -12985,7 +13034,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="157" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>36</v>
       </c>
@@ -13030,7 +13079,7 @@
       </c>
       <c r="Q157" s="2"/>
     </row>
-    <row r="158" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="158" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>36</v>
       </c>
@@ -13077,7 +13126,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="159" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>36</v>
       </c>
@@ -13124,7 +13173,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="160" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>36</v>
       </c>
@@ -13169,7 +13218,7 @@
       </c>
       <c r="Q160" s="2"/>
     </row>
-    <row r="161" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="161" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>36</v>
       </c>
@@ -13216,7 +13265,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="162" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>36</v>
       </c>
@@ -13261,7 +13310,7 @@
       </c>
       <c r="Q162" s="2"/>
     </row>
-    <row r="163" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="163" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>36</v>
       </c>
@@ -13306,7 +13355,7 @@
       </c>
       <c r="Q163" s="2"/>
     </row>
-    <row r="164" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="164" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>36</v>
       </c>
@@ -13353,7 +13402,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="11" customFormat="1" ht="28.7">
+    <row r="165" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>36</v>
       </c>
@@ -13397,6 +13446,194 @@
         <v>35</v>
       </c>
       <c r="Q165" s="2"/>
+    </row>
+    <row r="166" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J166" s="1"/>
+      <c r="K166" s="1"/>
+      <c r="L166" s="1"/>
+      <c r="M166" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="N166" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="O166" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="P166" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q166" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J167" s="1"/>
+      <c r="K167" s="1"/>
+      <c r="L167" s="1"/>
+      <c r="M167" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="N167" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="O167" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="P167" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q167" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J168" s="1"/>
+      <c r="K168" s="1"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="N168" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="O168" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="P168" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q168" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J169" s="1"/>
+      <c r="K169" s="1"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="N169" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="O169" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="P169" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q169" s="2" t="s">
+        <v>436</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R165" xr:uid="{BD0A80D8-6C04-4D44-A5DD-9337CFFA755D}"/>
@@ -13894,6 +14131,18 @@
     <hyperlink ref="D165" r:id="rId490" xr:uid="{A226491A-08BE-416F-86EA-17751F550CCC}"/>
     <hyperlink ref="E165" r:id="rId491" xr:uid="{6ABB6FCC-7F4F-445D-A6E0-E76F5D5331AF}"/>
     <hyperlink ref="N165" r:id="rId492" xr:uid="{A880BACA-067B-4608-B312-BEFB23759428}"/>
+    <hyperlink ref="D166" r:id="rId493" xr:uid="{36449EC9-553C-4DE9-A429-CF2030575A84}"/>
+    <hyperlink ref="E166" r:id="rId494" xr:uid="{6E927090-435B-4B25-8A2E-90F542A439D4}"/>
+    <hyperlink ref="N166" r:id="rId495" xr:uid="{E9E1790F-EE5E-4580-8A45-373EB557BAD6}"/>
+    <hyperlink ref="D167" r:id="rId496" xr:uid="{FF0E5D66-6DF8-4F45-A465-A469D80866CF}"/>
+    <hyperlink ref="E167" r:id="rId497" xr:uid="{B6D67FF8-5C0E-40A9-A115-07254EFBD73A}"/>
+    <hyperlink ref="N167" r:id="rId498" xr:uid="{CE01DA78-167D-4BB5-8B67-6D2A7552D02A}"/>
+    <hyperlink ref="D168" r:id="rId499" xr:uid="{05804AC1-8BB3-4723-B126-EC08D46A8D79}"/>
+    <hyperlink ref="E168" r:id="rId500" xr:uid="{0C7F473A-F0AA-4360-9EE3-A93D36303FFA}"/>
+    <hyperlink ref="N168" r:id="rId501" xr:uid="{AB369F7B-5658-44B7-9D14-A8E98B2255AF}"/>
+    <hyperlink ref="D169" r:id="rId502" xr:uid="{69BB11F8-995B-4198-9764-69F11BF78B74}"/>
+    <hyperlink ref="E169" r:id="rId503" xr:uid="{A1B9EFE0-BA4F-4CD4-A026-E14134EAE89D}"/>
+    <hyperlink ref="N169" r:id="rId504" xr:uid="{B385B923-E580-4E53-B2D5-4B9158E9A7B4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13902,17 +14151,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B11EE2-5871-4E08-84FC-BB1C5DE9909A}">
   <dimension ref="A1:AF1"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="10.17578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8203125" customWidth="1"/>
-    <col min="8" max="8" width="27.17578125" customWidth="1"/>
-    <col min="9" max="9" width="12.17578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24.29296875" customWidth="1"/>
-    <col min="21" max="21" width="12.9375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="8" width="27.140625" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.28515625" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" ht="14.1" customHeight="1">
+    <row r="1" spans="1:32" s="6" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
